--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.04390489679356</v>
+        <v>5.207134545728954</v>
       </c>
       <c r="D2" t="n">
-        <v>31.70451065862738</v>
+        <v>5.15198298202695</v>
       </c>
       <c r="E2" t="n">
-        <v>8.515592193122517</v>
+        <v>1.383783731382409</v>
       </c>
       <c r="F2" t="n">
-        <v>8.444788734989906</v>
+        <v>1.37227816943586</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.10989484154194</v>
+        <v>4.242857911750566</v>
       </c>
       <c r="D3" t="n">
-        <v>25.74400198045656</v>
+        <v>4.18340032182419</v>
       </c>
       <c r="E3" t="n">
-        <v>8.515592193122517</v>
+        <v>1.383783731382409</v>
       </c>
       <c r="F3" t="n">
-        <v>8.444788734989906</v>
+        <v>1.37227816943586</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.00374272262219</v>
+        <v>4.713108192426105</v>
       </c>
       <c r="D4" t="n">
-        <v>28.94894938319579</v>
+        <v>4.704204274769316</v>
       </c>
       <c r="E4" t="n">
-        <v>8.515592193122517</v>
+        <v>1.383783731382409</v>
       </c>
       <c r="F4" t="n">
-        <v>8.444788734989906</v>
+        <v>1.37227816943586</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.03721386143864</v>
+        <v>6.83104725248378</v>
       </c>
       <c r="D5" t="n">
-        <v>41.32157542647155</v>
+        <v>6.714756006801628</v>
       </c>
       <c r="E5" t="n">
-        <v>8.515592193122517</v>
+        <v>1.383783731382409</v>
       </c>
       <c r="F5" t="n">
-        <v>8.444788734989906</v>
+        <v>1.37227816943586</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.39192107505832</v>
+        <v>4.451187174696977</v>
       </c>
       <c r="D6" t="n">
-        <v>27.43360511526582</v>
+        <v>4.457960831230696</v>
       </c>
       <c r="E6" t="n">
-        <v>8.515592193122517</v>
+        <v>1.383783731382409</v>
       </c>
       <c r="F6" t="n">
-        <v>8.444788734989906</v>
+        <v>1.37227816943586</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.53244990342182</v>
+        <v>2.361523109306046</v>
       </c>
       <c r="D7" t="n">
-        <v>14.76406390436075</v>
+        <v>2.399160384458622</v>
       </c>
       <c r="E7" t="n">
-        <v>8.515592193122517</v>
+        <v>1.383783731382409</v>
       </c>
       <c r="F7" t="n">
-        <v>8.444788734989906</v>
+        <v>1.37227816943586</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.68134026537108</v>
+        <v>3.848217793122801</v>
       </c>
       <c r="D8" t="n">
-        <v>24.35925276452382</v>
+        <v>3.958378574235121</v>
       </c>
       <c r="E8" t="n">
-        <v>8.515592193122517</v>
+        <v>1.383783731382409</v>
       </c>
       <c r="F8" t="n">
-        <v>8.444788734989906</v>
+        <v>1.37227816943586</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>39.15240610708234</v>
+        <v>6.36226599240088</v>
       </c>
       <c r="D9" t="n">
-        <v>39.69183478377548</v>
+        <v>6.449923152363517</v>
       </c>
       <c r="E9" t="n">
-        <v>8.515592193122517</v>
+        <v>1.383783731382409</v>
       </c>
       <c r="F9" t="n">
-        <v>8.444788734989906</v>
+        <v>1.37227816943586</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.97253953050919</v>
+        <v>6.658037673707743</v>
       </c>
       <c r="D10" t="n">
-        <v>41.41388115382908</v>
+        <v>6.729755687497226</v>
       </c>
       <c r="E10" t="n">
-        <v>8.515592193122517</v>
+        <v>1.383783731382409</v>
       </c>
       <c r="F10" t="n">
-        <v>8.444788734989906</v>
+        <v>1.37227816943586</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
